--- a/data/homes4.xlsx
+++ b/data/homes4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\crm_bunyodkorhouse\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B86EA56A-8347-49E2-AB3F-585C941F9F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4365889F-6818-4F96-9205-09E6D0C5AC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6F381A45-3C0F-46F9-A926-09AC5934500A}"/>
   </bookViews>
@@ -94,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -192,11 +192,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,6 +230,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -533,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC060CB-8660-4A3E-8B04-8341A6CDB295}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.44140625" customWidth="1"/>
@@ -1171,6 +1193,74 @@
         <v>7000000</v>
       </c>
     </row>
+    <row r="38" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>-1</v>
+      </c>
+      <c r="B38" s="9">
+        <v>194</v>
+      </c>
+      <c r="C38" s="9">
+        <v>59</v>
+      </c>
+      <c r="D38" s="9">
+        <v>2</v>
+      </c>
+      <c r="E38" s="9">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="10">
+        <v>-1</v>
+      </c>
+      <c r="B39" s="5">
+        <v>195</v>
+      </c>
+      <c r="C39" s="5">
+        <v>62.5</v>
+      </c>
+      <c r="D39" s="5">
+        <v>2</v>
+      </c>
+      <c r="E39" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="10">
+        <v>-1</v>
+      </c>
+      <c r="B40" s="5">
+        <v>196</v>
+      </c>
+      <c r="C40" s="5">
+        <v>64</v>
+      </c>
+      <c r="D40" s="5">
+        <v>2</v>
+      </c>
+      <c r="E40" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="10">
+        <v>-1</v>
+      </c>
+      <c r="B41" s="5">
+        <v>197</v>
+      </c>
+      <c r="C41" s="5">
+        <v>59</v>
+      </c>
+      <c r="D41" s="5">
+        <v>2</v>
+      </c>
+      <c r="E41" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
